--- a/logs/post_logs.xlsx
+++ b/logs/post_logs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3831,6 +3831,96 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kid's Carnival</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>✅ Scheduled (Image)</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>DEMO_POST
+🔥 **DEMO DEALS OF THE DAY** 🔥
+💥 Price Crash Store
+⚡️ Up to 5% off
+👉🏻 amzaff.in/l3swo0g
+🌟 Kid's Carnival
+📣 Sale live till 28th July
+👉🏻 amzaff.in/jrtPYsT
+🧸 Toy's Fiesta
+⚡️ Up to 70% off...</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kid's Carnival</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>✅ Scheduled (Image)</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>DEMO_POST
+🔥 **DEMO DEALS OF THE DAY** 🔥
+💥 Price Crash Store
+⚡️ Up to 5% off
+👉🏻 amzaff.in/l3swo0g
+🌟 Kid's Carnival
+📣 Sale live till 28th July
+👉🏻 amzaff.in/jrtPYsT
+🧸 Toy's Fiesta
+⚡️ Up to 70% off...</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
